--- a/workspace/data/lead_scores.xlsx
+++ b/workspace/data/lead_scores.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,9 +33,13 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00333333"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -45,6 +49,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F2D3D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFDD00"/>
       </patternFill>
     </fill>
   </fills>
@@ -74,12 +88,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -445,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:L2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -521,6 +544,64 @@
       <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>LEAD-1750253100000</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18 07:25</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Hadi</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>+923362615506</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>xyz@gmail.com</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>King size 6ft by 6.5ft bed along with 2 side tables</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>general_interest</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Warm</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>new</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Wants to buy item 5978. King size bed with side tables at 85k.</t>
         </is>
       </c>
     </row>
@@ -543,12 +624,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Tier</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
@@ -581,7 +662,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -601,7 +682,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -612,7 +693,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-04-18 15:34:29</t>
+          <t>2026-06-18 07:25:28</t>
         </is>
       </c>
     </row>
